--- a/1_Data/Mcivor_2021_EJN/Codebook_Mcivor_2021_EJN_Exp1_Clean.xlsx
+++ b/1_Data/Mcivor_2021_EJN/Codebook_Mcivor_2021_EJN_Exp1_Clean.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,17 +485,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Block number 1-7 derived from the test-trial position per the paper's 6 x 150 + 60 structure (the merged export records no block information); NA for training trials</t>
+          <t>Task type: the kind of shape-label matching task performed in the trial (default self-matching; other tasks e.g. facialExpression-matching, monetaryValue-matching, self-pseudoWords)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1; 2; 3; 4; 5; 6; 7; NA (training)</t>
+          <t>self-matching</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -507,39 +507,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Trial</t>
+          <t>Phase</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Original trial index in the export (SubTrial 1-972; 1-12 training, 13-972 test)</t>
+          <t>Trial phase: training (12 trials; shapes and labels without faces) or test (960 trials)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Number (1-972)</t>
+          <t>training; test</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Numerical</t>
+          <t>Categorical</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Phase</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Trial phase: training (12 trials; shapes and labels without faces) or test (960 trials)</t>
+          <t>Block number 1-7 derived from the test-trial position per the paper's 6 x 150 + 60 structure (the merged export records no block information); NA for training trials</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>training; test</t>
+          <t>1; 2; 3; 4; 5; 6; 7; NA (training)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -551,39 +551,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Shape</t>
+          <t>Trial</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Geometric shape displayed (test rows from the recorded stimulus filename, e.g. Octagonhappy.jpg -&gt; Octagon; training rows derived from the design cell)</t>
+          <t>Original trial index in the export (SubTrial 1-972; 1-12 training, 13-972 test)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Circle; Triangle; Diamond; Pentagon; Hexagon; Octagon</t>
+          <t>Number (1-972)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Categorical</t>
+          <t>Numerical</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Label</t>
+          <t>Matching</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Label word displayed together with the shape</t>
+          <t>Whether the displayed shape matched its associated label</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Self; Other</t>
+          <t>Matching; Nonmatching</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -595,17 +595,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Shape</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Task type: the kind of shape-label matching task performed in the trial (default self-matching; other tasks e.g. facialExpression-matching, monetaryValue-matching, self-pseudoWords)</t>
+          <t>Geometric shape displayed (test rows from the recorded stimulus filename, e.g. Octagonhappy.jpg -&gt; Octagon; training rows derived from the design cell)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>self-matching</t>
+          <t>Circle; Triangle; Diamond; Pentagon; Hexagon; Octagon</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -617,17 +617,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Matching</t>
+          <t>Shape_Origin_Identity</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Whether the displayed shape matched its associated label</t>
+          <t>Shape name as recorded (the displayed geometric shape)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Matching; Nonmatching</t>
+          <t>Circle; Triangle; Diamond; Pentagon; Hexagon; Octagon</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -639,17 +639,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Label_Origin_Identity</t>
+          <t>Shape_English_Identity</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Label word as recorded</t>
+          <t>English shape name (identical to origin)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Self; Other</t>
+          <t>Circle; Triangle; Diamond; Pentagon; Hexagon; Octagon</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -661,17 +661,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Label_English_Identity</t>
+          <t>Shape_Standardized_Identity</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>English label (labels are already English; identical to origin)</t>
+          <t>Standardized identity of the displayed shape per the participant's binding: selfshape -&gt; Self; othershape -&gt; Stranger</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Self; Other</t>
+          <t>Self; Stranger</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -683,17 +683,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Label_Standardized_Identity</t>
+          <t>Label</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Standardized identity of the label: Self -&gt; Self; Other (an unknown other) -&gt; Stranger</t>
+          <t>Label word displayed together with the shape</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Self; Stranger</t>
+          <t>Self; Other</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -705,17 +705,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shape_Origin_Identity</t>
+          <t>Label_Origin_Identity</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shape name as recorded (the displayed geometric shape)</t>
+          <t>Label word as recorded</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Circle; Triangle; Diamond; Pentagon; Hexagon; Octagon</t>
+          <t>Self; Other</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -727,17 +727,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Shape_English_Identity</t>
+          <t>Label_English_Identity</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>English shape name (identical to origin)</t>
+          <t>English label (labels are already English; identical to origin)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Circle; Triangle; Diamond; Pentagon; Hexagon; Octagon</t>
+          <t>Self; Other</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -749,12 +749,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Shape_Standardized_Identity</t>
+          <t>Label_Standardized_Identity</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Standardized identity of the displayed shape per the participant's binding: selfshape -&gt; Self; othershape -&gt; Stranger</t>
+          <t>Standardized identity of the label: Self -&gt; Self; Other (an unknown other) -&gt; Stranger</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -793,17 +793,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>CorrResponse</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Actual key pressed</t>
+          <t>Correct response key for the trial (as designed; from raw CRESP/CorrectAnswer)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>s; k; NA (no response)</t>
+          <t>See per-study key mapping</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -815,39 +815,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RT_ms</t>
+          <t>Response</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Response time in ms from stimulus onset (CorrrT = ITI2.RT + 150 ms, verified); NA for no response and for one subject-9292 trial with a registered keypress but unrecorded RT; no RT filtering applied</t>
+          <t>Actual key pressed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ms (Number; 52-1149 for responded test trials; NA for no response)</t>
+          <t>s; k; NA (no response)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Numerical</t>
+          <t>Categorical</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RT_sec</t>
+          <t>RT_ms</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RT_ms / 1000 (seconds)</t>
+          <t>Response time in ms from stimulus onset (CorrrT = ITI2.RT + 150 ms, verified); NA for no response and for one subject-9292 trial with a registered keypress but unrecorded RT; no RT filtering applied</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>s (Number)</t>
+          <t>ms (Number; 52-1149 for responded test trials; NA for no response)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -859,20 +859,42 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>RT_sec</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>RT_ms / 1000 (seconds)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>s (Number)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Numerical</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>ACC</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Accuracy relative to the expected response key; no-response coded NA (the author file codes no-response as 0 and its ACC = (RESP == CRESP); the library ACC is recomputed as RESP == Correctanswer, identical on all rows)</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>1 (correct); 0 (incorrect key); NA (no response)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Categorical</t>
         </is>
